--- a/src/Verify.OpenXml.Tests/Samples.MultipleSheets.verified.xlsx
+++ b/src/Verify.OpenXml.Tests/Samples.MultipleSheets.verified.xlsx
@@ -117,23 +117,23 @@
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
-      <name val="Arial"/>
+      <name val="Aptos"/>
     </font>
     <font>
       <b/>
       <sz val="10"/>
-      <name val="Arial"/>
+      <name val="Aptos"/>
       <family val="2"/>
     </font>
     <font>
       <sz val="10"/>
-      <name val="Arial"/>
+      <name val="Aptos"/>
       <family val="2"/>
     </font>
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
-      <name val="Arial"/>
+      <name val="Aptos"/>
       <family val="2"/>
     </font>
   </fonts>

--- a/src/Verify.OpenXml.Tests/Samples.MultipleSheets.verified.xlsx
+++ b/src/Verify.OpenXml.Tests/Samples.MultipleSheets.verified.xlsx
@@ -715,5 +715,6 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait"/>
 </worksheet>
 </file>
--- a/src/Verify.OpenXml.Tests/Samples.MultipleSheets.verified.xlsx
+++ b/src/Verify.OpenXml.Tests/Samples.MultipleSheets.verified.xlsx
@@ -117,23 +117,23 @@
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
-      <name val="Arial"/>
+      <name val="Aptos"/>
     </font>
     <font>
       <b/>
       <sz val="10"/>
-      <name val="Arial"/>
+      <name val="Aptos"/>
       <family val="2"/>
     </font>
     <font>
       <sz val="10"/>
-      <name val="Arial"/>
+      <name val="Aptos"/>
       <family val="2"/>
     </font>
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
-      <name val="Arial"/>
+      <name val="Aptos"/>
       <family val="2"/>
     </font>
   </fonts>
@@ -715,5 +715,6 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait"/>
 </worksheet>
 </file>